--- a/output/full_scan/batch_seq0_2026-07-13.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-13.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8476</v>
+        <v>8261</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>566.2663539099013</v>
+        <v>570.8989191770751</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>22</v>
+        <v>292.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.19939291425085</v>
+        <v>58.81466050033401</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>49.19752417420064</v>
+        <v>54.32204328961171</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.295857231759208</v>
+        <v>0.3308579569134695</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.2940169721702821</v>
+        <v>2.20900730048529</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>9912</v>
+        <v>8476</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>550.1391329066755</v>
+        <v>566.2663539099013</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>12.55</v>
+        <v>22</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>48.89074197114165</v>
+        <v>51.19939291425085</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22.43846848135636</v>
+        <v>49.19752417420064</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.1065453797800834</v>
+        <v>1.295857231759208</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0125083958631287</v>
+        <v>-0.2940169721702821</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>9908</v>
+        <v>9912</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>538.1548711039131</v>
+        <v>550.1391329066755</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>29.85</v>
+        <v>12.55</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>57.08082921542496</v>
+        <v>48.89074197114165</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.66939827685805</v>
+        <v>22.43846848135636</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9774499311695282</v>
+        <v>0.1065453797800834</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0065727936887096</v>
+        <v>0.0125083958631287</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8071</v>
+        <v>9908</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>537.2728070724544</v>
+        <v>538.1548711039131</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.85</v>
+        <v>29.85</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>52.14049805651961</v>
+        <v>57.08082921542496</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>44.6062685108411</v>
+        <v>21.66939827685805</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3930359629025115</v>
+        <v>0.9774499311695282</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.4154872721978426</v>
+        <v>0.0065727936887096</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8481</v>
+        <v>8071</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>535.7409324310571</v>
+        <v>537.2728070724544</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>42.25</v>
+        <v>28.85</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.61776985551379</v>
+        <v>52.14049805651961</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15.37791387007381</v>
+        <v>44.6062685108411</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8090977624792465</v>
+        <v>0.3930359629025115</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0181912957783328</v>
+        <v>-0.4154872721978426</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9105</v>
+        <v>8481</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>524.5126998733451</v>
+        <v>535.7409324310571</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>42.25</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>47.71834387906793</v>
+        <v>62.61776985551379</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.43216819462072</v>
+        <v>15.37791387007381</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6743275135077919</v>
+        <v>0.8090977624792465</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.1841720358539907</v>
+        <v>0.0181912957783328</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8411</v>
+        <v>9105</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>524.3037180288637</v>
+        <v>524.5126998733451</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12.45</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.01580400481413</v>
+        <v>47.71834387906793</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.06649948050305</v>
+        <v>26.43216819462072</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6437019443661688</v>
+        <v>0.6743275135077919</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.040536347534136</v>
+        <v>-0.1841720358539907</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8222</v>
+        <v>8411</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>524.0565677203668</v>
+        <v>524.3037180288637</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>41.35</v>
+        <v>12.45</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>59.33649965617975</v>
+        <v>61.01580400481413</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.96487655950353</v>
+        <v>27.06649948050305</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.249202477895725</v>
+        <v>0.6437019443661688</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3583414025440183</v>
+        <v>0.040536347534136</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8105</v>
+        <v>8222</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>519.6576396939137</v>
+        <v>524.0565677203668</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>18.9</v>
+        <v>41.35</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>41.28564452271775</v>
+        <v>59.33649965617975</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.46205734303237</v>
+        <v>26.96487655950353</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4926055533663311</v>
+        <v>1.249202477895725</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.606785407993913</v>
+        <v>0.3583414025440183</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8069</v>
+        <v>8105</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>494.7688724344392</v>
+        <v>519.6576396939137</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>196</v>
+        <v>18.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45.36546792609678</v>
+        <v>41.28564452271775</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17.79309958276866</v>
+        <v>28.46205734303237</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4737869471141138</v>
+        <v>0.4926055533663311</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.010593557925044</v>
+        <v>-0.606785407993913</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8059</v>
+        <v>8069</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>491.283201319038</v>
+        <v>494.7688724344392</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17.4</v>
+        <v>196</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.12087468977505</v>
+        <v>45.36546792609678</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.44449623142498</v>
+        <v>17.79309958276866</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.00752942949567</v>
+        <v>0.4737869471141138</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0940011953803342</v>
+        <v>-1.010593557925044</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8466</v>
+        <v>8059</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>486.2795089086201</v>
+        <v>491.283201319038</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>64.70644732908788</v>
+        <v>51.12087468977505</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.8188965110124</v>
+        <v>21.44449623142498</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6034858858889417</v>
+        <v>2.00752942949567</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1122935101722952</v>
+        <v>0.0940011953803342</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8121</v>
+        <v>8466</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>478.7113770675143</v>
+        <v>486.2795089086201</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>41.8</v>
+        <v>17.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.53279467755259</v>
+        <v>64.70644732908788</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.77963356612244</v>
+        <v>30.8188965110124</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5132841274898471</v>
+        <v>0.6034858858889417</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.302724542965052</v>
+        <v>0.1122935101722952</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8093</v>
+        <v>8121</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>461.8099803959636</v>
+        <v>478.7113770675143</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19.7</v>
+        <v>41.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.07018402313135</v>
+        <v>43.53279467755259</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10.28182387435012</v>
+        <v>25.77963356612244</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.0664124545489764</v>
+        <v>0.5132841274898471</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0360082911201086</v>
+        <v>-1.302724542965052</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8163</v>
+        <v>8093</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>456.5478701906968</v>
+        <v>461.8099803959636</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>36.1</v>
+        <v>19.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>38.75947952378907</v>
+        <v>52.07018402313135</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26.50218599248986</v>
+        <v>10.28182387435012</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4813345047370164</v>
+        <v>0.0664124545489764</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.028146455190299</v>
+        <v>0.0360082911201086</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8081</v>
+        <v>8163</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>454.9200565299498</v>
+        <v>456.5478701906968</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>276.5</v>
+        <v>36.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>41.24561988217087</v>
+        <v>38.75947952378907</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.7445098538707</v>
+        <v>26.50218599248986</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7008238803846607</v>
+        <v>0.4813345047370164</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-5.440429571247881</v>
+        <v>-1.028146455190299</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8070</v>
+        <v>8081</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>443.5352860678009</v>
+        <v>454.9200565299498</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>52.4</v>
+        <v>276.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>43.76789075249372</v>
+        <v>41.24561988217087</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.85650620972973</v>
+        <v>22.7445098538707</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4819243667246739</v>
+        <v>0.7008238803846607</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.6182495177039586</v>
+        <v>-5.440429571247881</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8291</v>
+        <v>8070</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>443.0907212174365</v>
+        <v>443.5352860678009</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>28.5</v>
+        <v>52.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>30.12778210534988</v>
+        <v>43.76789075249372</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.49578568635711</v>
+        <v>18.85650620972973</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3658537311992163</v>
+        <v>0.4819243667246739</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.11238698434359</v>
+        <v>-0.6182495177039586</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8147</v>
+        <v>8291</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>440.3084215957896</v>
+        <v>443.0907212174365</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>145</v>
+        <v>28.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.0818597764921</v>
+        <v>30.12778210534988</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.70271248519719</v>
+        <v>29.49578568635711</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7317483987634589</v>
+        <v>0.3658537311992163</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.02215251869666</v>
+        <v>-1.11238698434359</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8438</v>
+        <v>8147</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>437.6582639216082</v>
+        <v>440.3084215957896</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>91.8</v>
+        <v>145</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.95842805090319</v>
+        <v>43.0818597764921</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.65570322291446</v>
+        <v>16.70271248519719</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3387576193030683</v>
+        <v>0.7317483987634589</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.5503769763826276</v>
+        <v>1.02215251869666</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>9911</v>
+        <v>8438</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>437.1197916029788</v>
+        <v>437.6582639216082</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>84.5</v>
+        <v>91.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.98633973415987</v>
+        <v>47.95842805090319</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>12.94448804525353</v>
+        <v>30.65570322291446</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.976492386179334</v>
+        <v>0.3387576193030683</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.07244173990086999</v>
+        <v>-0.5503769763826276</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8227</v>
+        <v>9911</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>434.1331535285716</v>
+        <v>437.1197916029788</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>175.5</v>
+        <v>84.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.05151756168428</v>
+        <v>55.98633973415987</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>13.11440874787061</v>
+        <v>12.94448804525353</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6729396410178022</v>
+        <v>0.976492386179334</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.793973851335369</v>
+        <v>0.07244173990086999</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8271</v>
+        <v>8227</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>430.4749584470218</v>
+        <v>434.1331535285716</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>183</v>
+        <v>175.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>38.08855942280526</v>
+        <v>42.05151756168428</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.65918424480648</v>
+        <v>13.11440874787061</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.813873831850914</v>
+        <v>0.6729396410178022</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.119929744364224</v>
+        <v>-1.793973851335369</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8374</v>
+        <v>8271</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>429.0725656595857</v>
+        <v>430.4749584470218</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>86.40000000000001</v>
+        <v>183</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>44.09064110825202</v>
+        <v>38.08855942280526</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11.8462958319241</v>
+        <v>22.65918424480648</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.073751722625995</v>
+        <v>0.813873831850914</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1226395962929092</v>
+        <v>-1.119929744364224</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8067</v>
+        <v>8374</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>421.2328415737011</v>
+        <v>429.0725656595857</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>13</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.90252907719683</v>
+        <v>44.09064110825202</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6.523371625091144</v>
+        <v>11.8462958319241</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2731790893577096</v>
+        <v>1.073751722625995</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.1042352575681522</v>
+        <v>-0.1226395962929092</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8454</v>
+        <v>8067</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>420.829017056744</v>
+        <v>421.2328415737011</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>262</v>
+        <v>13</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>41.08916869613203</v>
+        <v>49.90252907719683</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>28.61856562654848</v>
+        <v>6.523371625091144</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5059450882050776</v>
+        <v>0.2731790893577096</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-10.38905917629528</v>
+        <v>-0.1042352575681522</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8076</v>
+        <v>8454</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>411.3127496984529</v>
+        <v>420.829017056744</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>26.05</v>
+        <v>262</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.46796770904551</v>
+        <v>41.08916869613203</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.56743814406656</v>
+        <v>28.61856562654848</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9263947566364999</v>
+        <v>0.5059450882050776</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0655839336005505</v>
+        <v>-10.38905917629528</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8932</v>
+        <v>8076</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>401.257245677933</v>
+        <v>411.3127496984529</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>115</v>
+        <v>26.05</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.37063230877541</v>
+        <v>54.46796770904551</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.4888355047914</v>
+        <v>16.56743814406656</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6577467942910236</v>
+        <v>0.9263947566364999</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.9628180501180674</v>
+        <v>0.0655839336005505</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8443</v>
+        <v>8932</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>397.9855862553047</v>
+        <v>401.257245677933</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11.4</v>
+        <v>115</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.13949251823645</v>
+        <v>59.37063230877541</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>44.20906628137946</v>
+        <v>28.4888355047914</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.249813709979834</v>
+        <v>0.6577467942910236</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0007912044706774</v>
+        <v>0.9628180501180674</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8473</v>
+        <v>8443</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>391.3433205406806</v>
+        <v>397.9855862553047</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>45.1</v>
+        <v>11.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>39.72456336020495</v>
+        <v>46.13949251823645</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.73755521690476</v>
+        <v>44.20906628137946</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4544603444920799</v>
+        <v>0.249813709979834</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.878518624634601</v>
+        <v>0.0007912044706774</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8404</v>
+        <v>8473</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>391.333146677019</v>
+        <v>391.3433205406806</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>16.9</v>
+        <v>45.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.21497252754445</v>
+        <v>39.72456336020495</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.97650472762836</v>
+        <v>20.73755521690476</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.412632001891771</v>
+        <v>0.4544603444920799</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0424520844896692</v>
+        <v>-0.878518624634601</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8049</v>
+        <v>8404</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>389.0890549727914</v>
+        <v>391.333146677019</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>26.35</v>
+        <v>16.9</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>40.98012431059536</v>
+        <v>52.21497252754445</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.2365782571725</v>
+        <v>13.97650472762836</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3798942134165881</v>
+        <v>1.412632001891771</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1666654129401923</v>
+        <v>0.0424520844896692</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8442</v>
+        <v>8049</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>383.0956264960281</v>
+        <v>389.0890549727914</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>44</v>
+        <v>26.35</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.67074372873285</v>
+        <v>40.98012431059536</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>35.01921622423322</v>
+        <v>23.2365782571725</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.996788725870876</v>
+        <v>0.3798942134165881</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.6077477247233719</v>
+        <v>-0.1666654129401923</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8155</v>
+        <v>8442</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>377.0809245267632</v>
+        <v>383.0956264960281</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>342.5</v>
+        <v>44</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>35.93713787564886</v>
+        <v>56.67074372873285</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.42669166865042</v>
+        <v>35.01921622423322</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5661502513344713</v>
+        <v>0.996788725870876</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-3.983374988868809</v>
+        <v>0.6077477247233719</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8996</v>
+        <v>8155</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>376.7671159175931</v>
+        <v>377.0809245267632</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1240</v>
+        <v>342.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.19000113196269</v>
+        <v>35.93713787564886</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.72848585747134</v>
+        <v>17.42669166865042</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8355351749696089</v>
+        <v>0.5661502513344713</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-37.75182278846778</v>
+        <v>-3.983374988868809</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8390</v>
+        <v>8996</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>375.2060896537516</v>
+        <v>376.7671159175931</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.5</v>
+        <v>1240</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>39.84556808430239</v>
+        <v>44.19000113196269</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.2869761034788</v>
+        <v>17.72848585747134</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.107469199866727</v>
+        <v>0.8355351749696089</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.8832174890567881</v>
+        <v>-37.75182278846778</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8488</v>
+        <v>8390</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>373.3512239432304</v>
+        <v>375.2060896537516</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>102.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.11355401584133</v>
+        <v>39.84556808430239</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.67291554100951</v>
+        <v>22.2869761034788</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6.594282084546771</v>
+        <v>1.107469199866727</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1083251694621331</v>
+        <v>-0.8832174890567881</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8104</v>
+        <v>8488</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>371.1551760940423</v>
+        <v>373.3512239432304</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>40.6</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.35177525992072</v>
+        <v>51.11355401584133</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.23552679583728</v>
+        <v>12.67291554100951</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7631828681979246</v>
+        <v>6.594282084546771</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1315481617256846</v>
+        <v>0.1083251694621331</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8112</v>
+        <v>8104</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>358.1287126236338</v>
+        <v>371.1551760940423</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>87.5</v>
+        <v>40.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.51931255536228</v>
+        <v>54.35177525992072</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.55851247942997</v>
+        <v>21.23552679583728</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6517736681850494</v>
+        <v>0.7631828681979246</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.153626076464294</v>
+        <v>0.1315481617256846</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>9136</v>
+        <v>8112</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>352.7976026519027</v>
+        <v>358.1287126236338</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>12.8</v>
+        <v>87.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.7400414047292</v>
+        <v>44.51931255536228</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>26.89401909894896</v>
+        <v>16.55851247942997</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3415629613924238</v>
+        <v>0.6517736681850494</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.5817954888549536</v>
+        <v>-1.153626076464294</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8499</v>
+        <v>9136</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>346.5709659509184</v>
+        <v>352.7976026519027</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>284.5</v>
+        <v>12.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.80828353630874</v>
+        <v>44.7400414047292</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>14.04848600860486</v>
+        <v>26.89401909894896</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4978060289980771</v>
+        <v>0.3415629613924238</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-2.328862731906968</v>
+        <v>-0.5817954888549536</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8084</v>
+        <v>8499</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>342.5926922997098</v>
+        <v>346.5709659509184</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>47.05</v>
+        <v>284.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.51221395682561</v>
+        <v>43.80828353630874</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.66848257214059</v>
+        <v>14.04848600860486</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.283857475645913</v>
+        <v>0.4978060289980771</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2779365811116752</v>
+        <v>-2.328862731906968</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8103</v>
+        <v>8084</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>338.85324542903</v>
+        <v>342.5926922997098</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>89.2</v>
+        <v>47.05</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>37.07817760594232</v>
+        <v>44.51221395682561</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.76940057494709</v>
+        <v>17.66848257214059</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6518785522532398</v>
+        <v>3.283857475645913</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.6613889725601878</v>
+        <v>-0.2779365811116752</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8072</v>
+        <v>8103</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>328.9364876844609</v>
+        <v>338.85324542903</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>28.35</v>
+        <v>89.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.85166526772043</v>
+        <v>37.07817760594232</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.17188489631432</v>
+        <v>15.76940057494709</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5725809916310776</v>
+        <v>0.6518785522532398</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1603676096244268</v>
+        <v>-0.6613889725601878</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8367</v>
+        <v>8072</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>325.8311490793631</v>
+        <v>328.9364876844609</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>40.5</v>
+        <v>28.35</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.64705051243465</v>
+        <v>44.85166526772043</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.27717416493961</v>
+        <v>22.17188489631432</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5020717943826053</v>
+        <v>0.5725809916310776</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.09733627895010979</v>
+        <v>-0.1603676096244268</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>9907</v>
+        <v>8367</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>324.8801371259237</v>
+        <v>325.8311490793631</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>15.2</v>
+        <v>40.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>39.89296330847104</v>
+        <v>49.64705051243465</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>25.27647353414994</v>
+        <v>23.27717416493961</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6957046763819288</v>
+        <v>0.5020717943826053</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.009303634376888401</v>
+        <v>0.09733627895010979</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8064</v>
+        <v>9907</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>320.5751171646058</v>
+        <v>324.8801371259237</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>134.5</v>
+        <v>15.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.87340743984174</v>
+        <v>39.89296330847104</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.72415179157276</v>
+        <v>25.27647353414994</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.843161328642034</v>
+        <v>0.6957046763819288</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.464301706203241</v>
+        <v>0.009303634376888401</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8176</v>
+        <v>8064</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>319.4881410137699</v>
+        <v>320.5751171646058</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10.1</v>
+        <v>134.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,49 +3944,49 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45.54785833494895</v>
+        <v>46.87340743984174</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.12662605897257</v>
+        <v>19.72415179157276</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3111222699633414</v>
+        <v>1.843161328642034</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0005691763586569</v>
+        <v>-2.464301706203241</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8213</v>
+        <v>8176</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>316.0364711167565</v>
+        <v>319.4881410137699</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>34.2</v>
+        <v>10.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>37.44454061086418</v>
+        <v>45.54785833494895</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.96185494968869</v>
+        <v>22.12662605897257</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5865759812622138</v>
+        <v>0.3111222699633414</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.2160779646395358</v>
+        <v>0.0005691763586569</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8478</v>
+        <v>8213</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>313.4278817368337</v>
+        <v>316.0364711167565</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>156.5</v>
+        <v>34.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.83254649851411</v>
+        <v>37.44454061086418</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.53139993810856</v>
+        <v>15.96185494968869</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7658087628385569</v>
+        <v>0.5865759812622138</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.613502936002446</v>
+        <v>-0.2160779646395358</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8240</v>
+        <v>8478</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>310.583902620344</v>
+        <v>313.4278817368337</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>47.65</v>
+        <v>156.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>31.13073686627125</v>
+        <v>51.83254649851411</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.29657633760057</v>
+        <v>17.53139993810856</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6016949462377384</v>
+        <v>0.7658087628385569</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.3288898806298785</v>
+        <v>0.613502936002446</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8111</v>
+        <v>8240</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>308.8347592515585</v>
+        <v>310.583902620344</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>49.15</v>
+        <v>47.65</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>30.52307707849671</v>
+        <v>31.13073686627125</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.80345085870734</v>
+        <v>18.29657633760057</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.220883306937219</v>
+        <v>0.6016949462377384</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0145877517772672</v>
+        <v>-0.3288898806298785</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8215</v>
+        <v>8111</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>298.2977606382717</v>
+        <v>308.8347592515585</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>27.4</v>
+        <v>49.15</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.46711689430473</v>
+        <v>30.52307707849671</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.38419368590764</v>
+        <v>22.80345085870734</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4172688948423104</v>
+        <v>1.220883306937219</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.3082978917672152</v>
+        <v>0.0145877517772672</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8210</v>
+        <v>8215</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>298.0204649494672</v>
+        <v>298.2977606382717</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1135</v>
+        <v>27.4</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>34.45822679522244</v>
+        <v>42.46711689430473</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.28360133627356</v>
+        <v>19.38419368590764</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9915477486316168</v>
+        <v>0.4172688948423104</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-18.99284442929718</v>
+        <v>-0.3082978917672152</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8110</v>
+        <v>8210</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>297.4561365712313</v>
+        <v>298.0204649494672</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.8</v>
+        <v>1135</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>38.57475150306976</v>
+        <v>34.45822679522244</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.9988465008908</v>
+        <v>17.28360133627356</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3520106649189594</v>
+        <v>0.9915477486316168</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.055713499692519</v>
+        <v>-18.99284442929718</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8074</v>
+        <v>8110</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>295.7219951887213</v>
+        <v>297.4561365712313</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>62.5</v>
+        <v>48.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.82899393410614</v>
+        <v>38.57475150306976</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.50061462851852</v>
+        <v>13.9988465008908</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5401688241057939</v>
+        <v>0.3520106649189594</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.6649390231505437</v>
+        <v>-1.055713499692519</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8358</v>
+        <v>8074</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>293.6184546322968</v>
+        <v>295.7219951887213</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>498</v>
+        <v>62.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>40.11440990232234</v>
+        <v>36.82899393410614</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.7389066646331</v>
+        <v>16.50061462851852</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.058391352042575</v>
+        <v>0.5401688241057939</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-16.92678873339669</v>
+        <v>-0.6649390231505437</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8054</v>
+        <v>8358</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>290.6148298777557</v>
+        <v>293.6184546322968</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>97</v>
+        <v>498</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>38.39612633114328</v>
+        <v>40.11440990232234</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19.11280558982256</v>
+        <v>13.7389066646331</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3906461030351119</v>
+        <v>1.058391352042575</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.631224612110677</v>
+        <v>-16.92678873339669</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8086</v>
+        <v>8054</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>284.6125587142479</v>
+        <v>290.6148298777557</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.08693166109971</v>
+        <v>38.39612633114328</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.95211844844115</v>
+        <v>19.11280558982256</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6201104288053213</v>
+        <v>0.3906461030351119</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.637648765290776</v>
+        <v>-2.631224612110677</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8477</v>
+        <v>8086</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>282.1695234847081</v>
+        <v>284.6125587142479</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>15.9</v>
+        <v>135</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.63129894990355</v>
+        <v>38.08693166109971</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.20265879447297</v>
+        <v>13.95211844844115</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.618172083244613</v>
+        <v>0.6201104288053213</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1099580838786092</v>
+        <v>-1.637648765290776</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8114</v>
+        <v>8477</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>279.7597652086372</v>
+        <v>282.1695234847081</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>199.5</v>
+        <v>15.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.98359050688303</v>
+        <v>41.63129894990355</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.9448139662504</v>
+        <v>15.20265879447297</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5377727727078006</v>
+        <v>1.618172083244613</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.656955867767003</v>
+        <v>-0.1099580838786092</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8299</v>
+        <v>8114</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>273.108928448818</v>
+        <v>279.7597652086372</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>2170</v>
+        <v>199.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.92184975957623</v>
+        <v>45.98359050688303</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.48736727559869</v>
+        <v>19.9448139662504</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5658482351560855</v>
+        <v>0.5377727727078006</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-24.94503962775397</v>
+        <v>1.656955867767003</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8482</v>
+        <v>8299</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>263.9058477813055</v>
+        <v>273.108928448818</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>47.95</v>
+        <v>2170</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.47400341128972</v>
+        <v>42.92184975957623</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5.98987381666341</v>
+        <v>11.48736727559869</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.361252521371626</v>
+        <v>0.5658482351560855</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.423573454534133</v>
+        <v>-24.94503962775397</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9906</v>
+        <v>8482</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>257.8785188190709</v>
+        <v>263.9058477813055</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>40.1</v>
+        <v>47.95</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.42422679119637</v>
+        <v>51.47400341128972</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>30.41591765579264</v>
+        <v>5.98987381666341</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2895958590483775</v>
+        <v>1.361252521371626</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.4806958200055582</v>
+        <v>1.423573454534133</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8088</v>
+        <v>9906</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>256.1403681171789</v>
+        <v>257.8785188190709</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>53.6</v>
+        <v>40.1</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>35.94327972127962</v>
+        <v>45.42422679119637</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.93411307778187</v>
+        <v>30.41591765579264</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3258471567062068</v>
+        <v>0.2895958590483775</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.353862715476074</v>
+        <v>-0.4806958200055582</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>9904</v>
+        <v>8088</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>244.5486316037497</v>
+        <v>256.1403681171789</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>24.25</v>
+        <v>53.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>30.03324821605197</v>
+        <v>35.94327972127962</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23.16224659579787</v>
+        <v>17.93411307778187</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6264952825872622</v>
+        <v>0.3258471567062068</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1175130989562303</v>
+        <v>-1.353862715476074</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8422</v>
+        <v>9904</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>241.0587918990266</v>
+        <v>244.5486316037497</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>26.55</v>
+        <v>24.25</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>40.65938977893018</v>
+        <v>30.03324821605197</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.75313617997245</v>
+        <v>23.16224659579787</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8195192976387714</v>
+        <v>0.6264952825872622</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1671362849457125</v>
+        <v>-0.1175130989562303</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8048</v>
+        <v>8422</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>238.4536272194775</v>
+        <v>241.0587918990266</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>60.8</v>
+        <v>26.55</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.31075674228654</v>
+        <v>40.65938977893018</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10.98893963719153</v>
+        <v>11.75313617997245</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.454981126914189</v>
+        <v>0.8195192976387714</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.409372040139181</v>
+        <v>-0.1671362849457125</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8201</v>
+        <v>8048</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>235.5314738462089</v>
+        <v>238.4536272194775</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.85</v>
+        <v>60.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45.77192248027881</v>
+        <v>44.31075674228654</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.99035796028728</v>
+        <v>10.98893963719153</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.020111776372238</v>
+        <v>0.454981126914189</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0439069075455558</v>
+        <v>-0.409372040139181</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>9930</v>
+        <v>8201</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>226.6550141983857</v>
+        <v>235.5314738462089</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>63.1</v>
+        <v>12.85</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>24.97232490241852</v>
+        <v>45.77192248027881</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>43.34798178875572</v>
+        <v>15.99035796028728</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.365501419838572</v>
+        <v>1.020111776372238</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.3932090330707825</v>
+        <v>-0.0439069075455558</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8487</v>
+        <v>9930</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>222.52232474969</v>
+        <v>226.6550141983857</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>77</v>
+        <v>63.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.33585420470701</v>
+        <v>24.97232490241852</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.33576921395152</v>
+        <v>43.34798178875572</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.709877878006426</v>
+        <v>1.365501419838572</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.09285924346360661</v>
+        <v>-0.3932090330707825</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>9802</v>
+        <v>8487</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>216.9449351820484</v>
+        <v>222.52232474969</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>74.7</v>
+        <v>77</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.02930718249601</v>
+        <v>41.33585420470701</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.53990076334597</v>
+        <v>10.33576921395152</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8376548996043813</v>
+        <v>1.709877878006426</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1064014278874136</v>
+        <v>-0.09285924346360661</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8277</v>
+        <v>9802</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>208.1372553070609</v>
+        <v>216.9449351820484</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>8.24</v>
+        <v>74.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>36.78393746084967</v>
+        <v>48.02930718249601</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.01536192491952</v>
+        <v>13.53990076334597</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.517296111665005</v>
+        <v>0.8376548996043813</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.2961701858159191</v>
+        <v>0.1064014278874136</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8423</v>
+        <v>8277</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>204.0269707302389</v>
+        <v>208.1372553070609</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>17.55</v>
+        <v>8.24</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.3197349601154</v>
+        <v>36.78393746084967</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.34083591604451</v>
+        <v>26.01536192491952</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7228492136910268</v>
+        <v>0.517296111665005</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.004500679779558</v>
+        <v>-0.2961701858159191</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>9955</v>
+        <v>8423</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>201.3673995447</v>
+        <v>204.0269707302389</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>25.55</v>
+        <v>17.55</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>34.50688775558446</v>
+        <v>43.3197349601154</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>21.87411126913712</v>
+        <v>12.34083591604451</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.393864275448812</v>
+        <v>0.7228492136910268</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0022330016687782</v>
+        <v>0.004500679779558</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8341</v>
+        <v>9955</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>201.1002756250066</v>
+        <v>201.3673995447</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>76.2</v>
+        <v>25.55</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.68687260065925</v>
+        <v>34.50688775558446</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.6103833597714</v>
+        <v>21.87411126913712</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9203038627248794</v>
+        <v>1.393864275448812</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2172728215357775</v>
+        <v>-0.0022330016687782</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>9103</v>
+        <v>8341</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>198.8016477408481</v>
+        <v>201.1002756250066</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>4.97</v>
+        <v>76.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.22961388063261</v>
+        <v>41.68687260065925</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.39235826470223</v>
+        <v>16.6103833597714</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9164512194542616</v>
+        <v>0.9203038627248794</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0348507313003424</v>
+        <v>-0.2172728215357775</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8089</v>
+        <v>9103</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>198.4328924822941</v>
+        <v>198.8016477408481</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>20.1</v>
+        <v>4.97</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.7283629476145</v>
+        <v>40.22961388063261</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>28.86108798514822</v>
+        <v>14.39235826470223</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6572035910560874</v>
+        <v>0.9164512194542616</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0136577257248471</v>
+        <v>-0.0348507313003424</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8472</v>
+        <v>8089</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>198.3312108010248</v>
+        <v>198.4328924822941</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>78.8</v>
+        <v>20.1</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.22564554117512</v>
+        <v>45.7283629476145</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.8649936589034</v>
+        <v>28.86108798514822</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6619870486962401</v>
+        <v>0.6572035910560874</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.8493563540737225</v>
+        <v>0.0136577257248471</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8080</v>
+        <v>8472</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>195.8829969084556</v>
+        <v>198.3312108010248</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>27.55</v>
+        <v>78.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.96065112262347</v>
+        <v>43.22564554117512</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>43.61849588756638</v>
+        <v>14.8649936589034</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3273094938203574</v>
+        <v>0.6619870486962401</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0398446268151797</v>
+        <v>-0.8493563540737225</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8431</v>
+        <v>8080</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>178.7249138428123</v>
+        <v>195.8829969084556</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>48.85</v>
+        <v>27.55</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.74455418772507</v>
+        <v>43.96065112262347</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.45289899009442</v>
+        <v>43.61849588756638</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.022082304454893</v>
+        <v>0.3273094938203574</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.2356421404389499</v>
+        <v>-0.0398446268151797</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>9110</v>
+        <v>8431</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>169.4477249599269</v>
+        <v>178.7249138428123</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>3.13</v>
+        <v>48.85</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.56860436973093</v>
+        <v>36.74455418772507</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>10.21299209384728</v>
+        <v>11.45289899009442</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4800940984432949</v>
+        <v>1.022082304454893</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0344141562468925</v>
+        <v>-0.2356421404389499</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8087</v>
+        <v>9110</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>169.0229567562166</v>
+        <v>169.4477249599269</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>31</v>
+        <v>3.13</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.77784397115088</v>
+        <v>50.56860436973093</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.782453003837922</v>
+        <v>10.21299209384728</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2186926180359017</v>
+        <v>0.4800940984432949</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1740327525353027</v>
+        <v>0.0344141562468925</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8440</v>
+        <v>8087</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>166.8151438065508</v>
+        <v>169.0229567562166</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>21.05</v>
+        <v>31</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.8290862479945</v>
+        <v>36.77784397115088</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8.770465844695231</v>
+        <v>9.782453003837922</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6412672615929862</v>
+        <v>0.2186926180359017</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0392198489630606</v>
+        <v>-0.1740327525353027</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8429</v>
+        <v>8440</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>165.9094633823</v>
+        <v>166.8151438065508</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>6.22</v>
+        <v>21.05</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.5470826001446</v>
+        <v>39.8290862479945</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.44667613269461</v>
+        <v>8.770465844695231</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6395229728586289</v>
+        <v>0.6412672615929862</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0073586655168978</v>
+        <v>-0.0392198489630606</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>9902</v>
+        <v>8429</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>161.6915687947878</v>
+        <v>165.9094633823</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>13.8</v>
+        <v>6.22</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.40957949838931</v>
+        <v>41.5470826001446</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.21779044215514</v>
+        <v>13.44667613269461</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.08058208289134</v>
+        <v>0.6395229728586289</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0343568139020946</v>
+        <v>-0.0073586655168978</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8249</v>
+        <v>9902</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>153.4788114419316</v>
+        <v>161.6915687947878</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>47.1</v>
+        <v>13.8</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>38.76180618266233</v>
+        <v>49.40957949838931</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.17658028795427</v>
+        <v>17.21779044215514</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3812305704638479</v>
+        <v>1.08058208289134</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1787161149507308</v>
+        <v>0.0343568139020946</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8455</v>
+        <v>8249</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>152.0722546070916</v>
+        <v>153.4788114419316</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>26.5</v>
+        <v>47.1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.28964550193269</v>
+        <v>38.76180618266233</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.19289433906141</v>
+        <v>14.17658028795427</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5872568588313569</v>
+        <v>0.3812305704638479</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1187848741253774</v>
+        <v>-0.1787161149507308</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>9910</v>
+        <v>8455</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>151.1580013139594</v>
+        <v>152.0722546070916</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.99209145187846</v>
+        <v>39.28964550193269</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>18.60864235786543</v>
+        <v>18.19289433906141</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3077558034073349</v>
+        <v>0.5872568588313569</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.421881380858031</v>
+        <v>-0.1187848741253774</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8940</v>
+        <v>9910</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>149.782026268778</v>
+        <v>151.1580013139594</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>16.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.2545682416612</v>
+        <v>39.99209145187846</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.94793245052318</v>
+        <v>18.60864235786543</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4994305882762038</v>
+        <v>0.3077558034073349</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0104152734138692</v>
+        <v>-0.421881380858031</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8171</v>
+        <v>8940</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>147.2811325316508</v>
+        <v>149.782026268778</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>20.45</v>
+        <v>16.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>39.66852283727286</v>
+        <v>39.2545682416612</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.59135447160642</v>
+        <v>17.94793245052318</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5051443164399427</v>
+        <v>0.4994305882762038</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0072590402185457</v>
+        <v>-0.0104152734138692</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8097</v>
+        <v>8171</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>133.1725353836445</v>
+        <v>147.2811325316508</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>56.2</v>
+        <v>20.45</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.29709471556058</v>
+        <v>39.66852283727286</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.18703668512312</v>
+        <v>18.59135447160642</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4175774088573503</v>
+        <v>0.5051443164399427</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.4151082822739262</v>
+        <v>-0.0072590402185457</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8068</v>
+        <v>8097</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>124.271709522876</v>
+        <v>133.1725353836445</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>18.2</v>
+        <v>56.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.71096966756419</v>
+        <v>40.29709471556058</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.02878131373818</v>
+        <v>15.18703668512312</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.701113412677411</v>
+        <v>0.4175774088573503</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0132248130369458</v>
+        <v>-0.4151082822739262</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8092</v>
+        <v>8068</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>114.4913258759912</v>
+        <v>124.271709522876</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>13.7</v>
+        <v>18.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.22624877796002</v>
+        <v>38.71096966756419</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.32250126357352</v>
+        <v>16.02878131373818</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4672127731244017</v>
+        <v>0.701113412677411</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0688251111663635</v>
+        <v>0.0132248130369458</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8085</v>
+        <v>8092</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>109.3212204761604</v>
+        <v>114.4913258759912</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.55237072283545</v>
+        <v>38.22624877796002</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.01021416169046</v>
+        <v>15.32250126357352</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8262659878586581</v>
+        <v>0.4672127731244017</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0074076444104546</v>
+        <v>0.0688251111663635</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8463</v>
+        <v>8085</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>96.73264084397113</v>
+        <v>109.3212204761604</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>21.2</v>
+        <v>11.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.76080599709727</v>
+        <v>43.55237072283545</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.97691959208202</v>
+        <v>16.01021416169046</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.783070955127068</v>
+        <v>0.8262659878586581</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0029802671646632</v>
+        <v>-0.0074076444104546</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8101</v>
+        <v>8463</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>95.83436957858019</v>
+        <v>96.73264084397113</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>13.15</v>
+        <v>21.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.33914650744629</v>
+        <v>39.76080599709727</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11.87221625038327</v>
+        <v>11.97691959208202</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6297268567379021</v>
+        <v>0.783070955127068</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0840647971391856</v>
+        <v>0.0029802671646632</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8467</v>
+        <v>8101</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>83.09522205505307</v>
+        <v>95.83436957858019</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>110</v>
+        <v>13.15</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45.05283021414026</v>
+        <v>44.33914650744629</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>10.20125102467581</v>
+        <v>11.87221625038327</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6668686595823127</v>
+        <v>0.6297268567379021</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0578350645365675</v>
+        <v>-0.0840647971391856</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,52 +6622,105 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
+        <v>8467</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>波力-KY</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>83.09522205505307</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>45.05283021414026</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>10.20125102467581</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.6668686595823127</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0578350645365675</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>8410</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>森田</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>59.74223410555582</v>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>32.75</v>
       </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>41.68044354946561</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>14.13139310337191</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>0.4304693840542011</v>
       </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>0.0586811531735191</v>
       </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
